--- a/artfynd/A 21769-2023 artfynd.xlsx
+++ b/artfynd/A 21769-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21769-2023 artfynd.xlsx
+++ b/artfynd/A 21769-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6897518</v>
+        <v>2692712</v>
       </c>
       <c r="B2" t="n">
-        <v>100516</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>225046</v>
+        <v>219864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Näs, Bl</t>
+          <t>Östra Näsnabben, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474616.0797815366</v>
+        <v>474524</v>
       </c>
       <c r="R2" t="n">
-        <v>6208701.576762941</v>
+        <v>6208609</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -741,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-07-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-05-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-07-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-05-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,6 +771,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -780,6 +788,99 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6897518</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västra Näs, Bl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>474616</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6208702</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sölvesborg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mjällby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2013-07-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2013-07-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
